--- a/public/ecommerce_departments_all_jobs_completed.xlsx
+++ b/public/ecommerce_departments_all_jobs_completed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Ecommerce\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{B8A11120-83FE-42D2-B386-BA211816B29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{811BD511-5667-42D5-A653-FC113AD87ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3320,7 +3320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3334,6 +3334,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3690,7 +3693,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -3708,7 +3711,7 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
